--- a/Reference Functions (3).xlsx
+++ b/Reference Functions (3).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MIHIR\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MIHIR\Desktop\Excel Dmart data Analyst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F142FAC3-D34D-4281-B949-71BFAFA7AC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{220C8D43-37DD-418D-91E3-C8004F6DFB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{F96F1919-2E57-49E2-86D2-F7D4BC614325}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{F96F1919-2E57-49E2-86D2-F7D4BC614325}"/>
   </bookViews>
   <sheets>
     <sheet name="Vlookup" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="287">
   <si>
     <t>LOOKUP TABLES</t>
   </si>
@@ -937,6 +937,12 @@
   <si>
     <t>salary</t>
   </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
+  </si>
 </sst>
 </file>
 
@@ -945,7 +951,7 @@
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="[$£-809]#,##0.00;\-[$£-809]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="[$£-809]#,##0.00;\-[$£-809]#,##0.00"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -1505,7 +1511,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1651,13 +1657,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1675,8 +1678,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2115,13 +2122,13 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B3" s="4"/>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
       <c r="H3" s="5"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.35">
@@ -2215,7 +2222,7 @@
       <c r="J8" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="72">
         <f>VLOOKUP(Destination,BasePrices,2,FALSE)</f>
         <v>411</v>
       </c>
@@ -2393,12 +2400,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="77"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="76"/>
       <c r="E1" s="28"/>
       <c r="F1" s="28"/>
       <c r="G1" s="28"/>
@@ -3010,6 +3017,12 @@
       <c r="E41" s="46" t="s">
         <v>119</v>
       </c>
+      <c r="G41" s="46" t="s">
+        <v>285</v>
+      </c>
+      <c r="H41" s="46" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C42" s="46">
@@ -3020,6 +3033,13 @@
       </c>
       <c r="E42" s="46" t="s">
         <v>121</v>
+      </c>
+      <c r="G42" s="46">
+        <v>76</v>
+      </c>
+      <c r="H42" s="46" t="str">
+        <f>VLOOKUP(G42,Table1[],3,TRUE)</f>
+        <v>B</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -3159,7 +3179,10 @@
       <c r="D4" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="E4" s="46"/>
+      <c r="E4" s="78">
+        <f>HLOOKUP(D4,$J$4:$O$5,2,TRUE)</f>
+        <v>46341</v>
+      </c>
       <c r="F4" s="56">
         <v>0.4375</v>
       </c>
@@ -3199,7 +3222,10 @@
       <c r="D5" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="46"/>
+      <c r="E5" s="78">
+        <f t="shared" ref="E5:E23" si="0">HLOOKUP(D5,$J$4:$O$5,2,TRUE)</f>
+        <v>46338</v>
+      </c>
       <c r="F5" s="56">
         <v>0.41666666666666669</v>
       </c>
@@ -3207,12 +3233,24 @@
       <c r="I5" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="58"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
+      <c r="J5" s="58">
+        <v>46336</v>
+      </c>
+      <c r="K5" s="58">
+        <v>46337</v>
+      </c>
+      <c r="L5" s="58">
+        <v>46338</v>
+      </c>
+      <c r="M5" s="58">
+        <v>46339</v>
+      </c>
+      <c r="N5" s="58">
+        <v>46340</v>
+      </c>
+      <c r="O5" s="58">
+        <v>46341</v>
+      </c>
     </row>
     <row r="6" spans="1:15" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A6" s="54" t="s">
@@ -3227,7 +3265,10 @@
       <c r="D6" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="E6" s="46"/>
+      <c r="E6" s="78">
+        <f t="shared" si="0"/>
+        <v>46339</v>
+      </c>
       <c r="F6" s="56">
         <v>0.58333333333333337</v>
       </c>
@@ -3253,7 +3294,10 @@
       <c r="D7" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="46"/>
+      <c r="E7" s="78">
+        <f t="shared" si="0"/>
+        <v>46338</v>
+      </c>
       <c r="F7" s="56">
         <v>0.4375</v>
       </c>
@@ -3279,7 +3323,10 @@
       <c r="D8" s="55" t="s">
         <v>140</v>
       </c>
-      <c r="E8" s="46"/>
+      <c r="E8" s="78">
+        <f t="shared" si="0"/>
+        <v>46336</v>
+      </c>
       <c r="F8" s="56">
         <v>0.41666666666666669</v>
       </c>
@@ -3305,7 +3352,10 @@
       <c r="D9" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="46"/>
+      <c r="E9" s="78">
+        <f t="shared" si="0"/>
+        <v>46340</v>
+      </c>
       <c r="F9" s="56">
         <v>0.45833333333333331</v>
       </c>
@@ -3331,7 +3381,10 @@
       <c r="D10" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="E10" s="46"/>
+      <c r="E10" s="78">
+        <f t="shared" si="0"/>
+        <v>46341</v>
+      </c>
       <c r="F10" s="56">
         <v>0.47916666666666669</v>
       </c>
@@ -3357,7 +3410,10 @@
       <c r="D11" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="46"/>
+      <c r="E11" s="78">
+        <f t="shared" si="0"/>
+        <v>46338</v>
+      </c>
       <c r="F11" s="56">
         <v>0.47916666666666669</v>
       </c>
@@ -3383,7 +3439,10 @@
       <c r="D12" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="46"/>
+      <c r="E12" s="78">
+        <f t="shared" si="0"/>
+        <v>46338</v>
+      </c>
       <c r="F12" s="56">
         <v>0.52083333333333337</v>
       </c>
@@ -3409,7 +3468,10 @@
       <c r="D13" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="E13" s="46"/>
+      <c r="E13" s="78">
+        <f t="shared" si="0"/>
+        <v>46337</v>
+      </c>
       <c r="F13" s="56">
         <v>0.58333333333333337</v>
       </c>
@@ -3435,7 +3497,10 @@
       <c r="D14" s="55" t="s">
         <v>140</v>
       </c>
-      <c r="E14" s="46"/>
+      <c r="E14" s="78">
+        <f t="shared" si="0"/>
+        <v>46336</v>
+      </c>
       <c r="F14" s="56">
         <v>0.44444444444444442</v>
       </c>
@@ -3461,7 +3526,10 @@
       <c r="D15" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="E15" s="46"/>
+      <c r="E15" s="78">
+        <f t="shared" si="0"/>
+        <v>46340</v>
+      </c>
       <c r="F15" s="56">
         <v>0.5</v>
       </c>
@@ -3487,7 +3555,10 @@
       <c r="D16" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="E16" s="46"/>
+      <c r="E16" s="78">
+        <f t="shared" si="0"/>
+        <v>46340</v>
+      </c>
       <c r="F16" s="56">
         <v>0.60416666666666663</v>
       </c>
@@ -3513,7 +3584,10 @@
       <c r="D17" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="E17" s="46"/>
+      <c r="E17" s="78">
+        <f t="shared" si="0"/>
+        <v>46337</v>
+      </c>
       <c r="F17" s="56">
         <v>0.61111111111111105</v>
       </c>
@@ -3539,7 +3613,10 @@
       <c r="D18" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="E18" s="46"/>
+      <c r="E18" s="78">
+        <f t="shared" si="0"/>
+        <v>46341</v>
+      </c>
       <c r="F18" s="56">
         <v>0.58333333333333337</v>
       </c>
@@ -3565,7 +3642,10 @@
       <c r="D19" s="55" t="s">
         <v>140</v>
       </c>
-      <c r="E19" s="46"/>
+      <c r="E19" s="78">
+        <f t="shared" si="0"/>
+        <v>46336</v>
+      </c>
       <c r="F19" s="56">
         <v>0.47222222222222227</v>
       </c>
@@ -3591,7 +3671,10 @@
       <c r="D20" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="E20" s="46"/>
+      <c r="E20" s="78">
+        <f t="shared" si="0"/>
+        <v>46339</v>
+      </c>
       <c r="F20" s="56">
         <v>0.60416666666666663</v>
       </c>
@@ -3617,7 +3700,10 @@
       <c r="D21" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="E21" s="46"/>
+      <c r="E21" s="78">
+        <f t="shared" si="0"/>
+        <v>46339</v>
+      </c>
       <c r="F21" s="56">
         <v>0.63888888888888895</v>
       </c>
@@ -3643,7 +3729,10 @@
       <c r="D22" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="E22" s="46"/>
+      <c r="E22" s="78">
+        <f t="shared" si="0"/>
+        <v>46341</v>
+      </c>
       <c r="F22" s="56">
         <v>0.625</v>
       </c>
@@ -3669,7 +3758,10 @@
       <c r="D23" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="46"/>
+      <c r="E23" s="78">
+        <f t="shared" si="0"/>
+        <v>46338</v>
+      </c>
       <c r="F23" s="56">
         <v>0.60416666666666663</v>
       </c>
@@ -3736,276 +3828,281 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="79" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="79" t="s">
         <v>221</v>
       </c>
-      <c r="C1" s="71" t="s">
+      <c r="C1" s="79" t="s">
         <v>222</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="79" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="72">
+      <c r="A2" s="80">
         <v>1001</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="80" t="s">
         <v>224</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="D2" s="72">
+      <c r="D2" s="80">
         <v>35000</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="72">
+      <c r="A3" s="80">
         <v>1002</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="80" t="s">
         <v>226</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="80" t="s">
         <v>227</v>
       </c>
-      <c r="D3" s="72">
+      <c r="D3" s="80">
         <v>40000</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="72">
+      <c r="A4" s="80">
         <v>1003</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="80" t="s">
         <v>228</v>
       </c>
-      <c r="C4" s="72" t="s">
+      <c r="C4" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="D4" s="72">
+      <c r="D4" s="80">
         <v>45000</v>
       </c>
-      <c r="F4" s="73" t="s">
+      <c r="F4" s="71" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="72">
+      <c r="A5" s="80">
         <v>1004</v>
       </c>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="80" t="s">
         <v>230</v>
       </c>
-      <c r="C5" s="72" t="s">
+      <c r="C5" s="80" t="s">
         <v>231</v>
       </c>
-      <c r="D5" s="72">
+      <c r="D5" s="80">
         <v>42000</v>
       </c>
-      <c r="F5" s="46"/>
+      <c r="F5" s="46" t="str">
+        <f>VLOOKUP(A25,$A$2:$D$51,2,FALSE)</f>
+        <v>Nisha</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="72">
+      <c r="A6" s="80">
         <v>1005</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="80" t="s">
         <v>232</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="D6" s="72">
+      <c r="D6" s="80">
         <v>38000</v>
       </c>
       <c r="F6" s="46"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="72">
+      <c r="A7" s="80">
         <v>1006</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="80" t="s">
         <v>233</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="D7" s="72">
+      <c r="D7" s="80">
         <v>46000</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="72">
+      <c r="A8" s="80">
         <v>1007</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="80" t="s">
         <v>234</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="80" t="s">
         <v>227</v>
       </c>
-      <c r="D8" s="72">
+      <c r="D8" s="80">
         <v>39000</v>
       </c>
-      <c r="F8" s="73" t="s">
+      <c r="F8" s="71" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="72">
+      <c r="A9" s="80">
         <v>1008</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="80" t="s">
         <v>235</v>
       </c>
-      <c r="C9" s="72" t="s">
+      <c r="C9" s="80" t="s">
         <v>231</v>
       </c>
-      <c r="D9" s="72">
+      <c r="D9" s="80">
         <v>44000</v>
       </c>
-      <c r="F9" s="46"/>
+      <c r="F9" s="46" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="72">
+      <c r="A10" s="80">
         <v>1009</v>
       </c>
-      <c r="B10" s="72" t="s">
+      <c r="B10" s="80" t="s">
         <v>236</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="C10" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="D10" s="72">
+      <c r="D10" s="80">
         <v>48000</v>
       </c>
       <c r="F10" s="46"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="72">
+      <c r="A11" s="80">
         <v>1010</v>
       </c>
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="80" t="s">
         <v>237</v>
       </c>
-      <c r="C11" s="72" t="s">
+      <c r="C11" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="D11" s="72">
+      <c r="D11" s="80">
         <v>37000</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="72">
+      <c r="A12" s="80">
         <v>1011</v>
       </c>
-      <c r="B12" s="72" t="s">
+      <c r="B12" s="80" t="s">
         <v>238</v>
       </c>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="80" t="s">
         <v>227</v>
       </c>
-      <c r="D12" s="72">
+      <c r="D12" s="80">
         <v>41000</v>
       </c>
-      <c r="F12" s="73" t="s">
+      <c r="F12" s="71" t="s">
         <v>280</v>
       </c>
-      <c r="H12" s="73" t="s">
+      <c r="H12" s="71" t="s">
         <v>282</v>
       </c>
-      <c r="I12" s="73" t="s">
+      <c r="I12" s="71" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="72">
+      <c r="A13" s="80">
         <v>1012</v>
       </c>
-      <c r="B13" s="72" t="s">
+      <c r="B13" s="80" t="s">
         <v>239</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="80" t="s">
         <v>231</v>
       </c>
-      <c r="D13" s="72">
+      <c r="D13" s="80">
         <v>43000</v>
       </c>
       <c r="H13" s="46"/>
       <c r="I13" s="46"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="72">
+      <c r="A14" s="80">
         <v>1013</v>
       </c>
-      <c r="B14" s="72" t="s">
+      <c r="B14" s="80" t="s">
         <v>240</v>
       </c>
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="D14" s="72">
+      <c r="D14" s="80">
         <v>47000</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="72">
+      <c r="A15" s="80">
         <v>1014</v>
       </c>
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="80" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="D15" s="72">
+      <c r="D15" s="80">
         <v>36000</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="72">
+      <c r="A16" s="80">
         <v>1015</v>
       </c>
-      <c r="B16" s="72" t="s">
+      <c r="B16" s="80" t="s">
         <v>242</v>
       </c>
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="80" t="s">
         <v>227</v>
       </c>
-      <c r="D16" s="72">
+      <c r="D16" s="80">
         <v>40000</v>
       </c>
-      <c r="F16" s="73" t="s">
+      <c r="F16" s="71" t="s">
         <v>281</v>
       </c>
-      <c r="H16" s="73" t="s">
+      <c r="H16" s="71" t="s">
         <v>282</v>
       </c>
-      <c r="I16" s="73" t="s">
+      <c r="I16" s="71" t="s">
         <v>283</v>
       </c>
-      <c r="J16" s="73" t="s">
+      <c r="J16" s="71" t="s">
         <v>222</v>
       </c>
-      <c r="K16" s="73" t="s">
+      <c r="K16" s="71" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A17" s="72">
+      <c r="A17" s="80">
         <v>1016</v>
       </c>
-      <c r="B17" s="72" t="s">
+      <c r="B17" s="80" t="s">
         <v>243</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="D17" s="72">
+      <c r="D17" s="80">
         <v>49000</v>
       </c>
       <c r="H17" s="46"/>
@@ -4014,478 +4111,478 @@
       <c r="K17" s="46"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A18" s="72">
+      <c r="A18" s="80">
         <v>1017</v>
       </c>
-      <c r="B18" s="72" t="s">
+      <c r="B18" s="80" t="s">
         <v>244</v>
       </c>
-      <c r="C18" s="72" t="s">
+      <c r="C18" s="80" t="s">
         <v>231</v>
       </c>
-      <c r="D18" s="72">
+      <c r="D18" s="80">
         <v>45000</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A19" s="72">
+      <c r="A19" s="80">
         <v>1018</v>
       </c>
-      <c r="B19" s="72" t="s">
+      <c r="B19" s="80" t="s">
         <v>245</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="D19" s="72">
+      <c r="D19" s="80">
         <v>38000</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A20" s="72">
+      <c r="A20" s="80">
         <v>1019</v>
       </c>
-      <c r="B20" s="72" t="s">
+      <c r="B20" s="80" t="s">
         <v>246</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="80" t="s">
         <v>227</v>
       </c>
-      <c r="D20" s="72">
+      <c r="D20" s="80">
         <v>42000</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A21" s="72">
+      <c r="A21" s="80">
         <v>1020</v>
       </c>
-      <c r="B21" s="72" t="s">
+      <c r="B21" s="80" t="s">
         <v>247</v>
       </c>
-      <c r="C21" s="72" t="s">
+      <c r="C21" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="D21" s="72">
+      <c r="D21" s="80">
         <v>50000</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A22" s="72">
+      <c r="A22" s="80">
         <v>1021</v>
       </c>
-      <c r="B22" s="72" t="s">
+      <c r="B22" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="80" t="s">
         <v>231</v>
       </c>
-      <c r="D22" s="72">
+      <c r="D22" s="80">
         <v>46000</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A23" s="72">
+      <c r="A23" s="80">
         <v>1022</v>
       </c>
-      <c r="B23" s="72" t="s">
+      <c r="B23" s="80" t="s">
         <v>249</v>
       </c>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="D23" s="72">
+      <c r="D23" s="80">
         <v>39000</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A24" s="72">
+      <c r="A24" s="80">
         <v>1023</v>
       </c>
-      <c r="B24" s="72" t="s">
+      <c r="B24" s="80" t="s">
         <v>250</v>
       </c>
-      <c r="C24" s="72" t="s">
+      <c r="C24" s="80" t="s">
         <v>227</v>
       </c>
-      <c r="D24" s="72">
+      <c r="D24" s="80">
         <v>43000</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A25" s="72">
+      <c r="A25" s="80">
         <v>1024</v>
       </c>
-      <c r="B25" s="72" t="s">
+      <c r="B25" s="80" t="s">
         <v>251</v>
       </c>
-      <c r="C25" s="72" t="s">
+      <c r="C25" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="D25" s="72">
+      <c r="D25" s="80">
         <v>51000</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A26" s="72">
+      <c r="A26" s="80">
         <v>1025</v>
       </c>
-      <c r="B26" s="72" t="s">
+      <c r="B26" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="C26" s="72" t="s">
+      <c r="C26" s="80" t="s">
         <v>231</v>
       </c>
-      <c r="D26" s="72">
+      <c r="D26" s="80">
         <v>47000</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A27" s="72">
+      <c r="A27" s="80">
         <v>1026</v>
       </c>
-      <c r="B27" s="72" t="s">
+      <c r="B27" s="80" t="s">
         <v>253</v>
       </c>
-      <c r="C27" s="72" t="s">
+      <c r="C27" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="D27" s="72">
+      <c r="D27" s="80">
         <v>40000</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A28" s="72">
+      <c r="A28" s="80">
         <v>1027</v>
       </c>
-      <c r="B28" s="72" t="s">
+      <c r="B28" s="80" t="s">
         <v>254</v>
       </c>
-      <c r="C28" s="72" t="s">
+      <c r="C28" s="80" t="s">
         <v>227</v>
       </c>
-      <c r="D28" s="72">
+      <c r="D28" s="80">
         <v>44000</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A29" s="72">
+      <c r="A29" s="80">
         <v>1028</v>
       </c>
-      <c r="B29" s="72" t="s">
+      <c r="B29" s="80" t="s">
         <v>255</v>
       </c>
-      <c r="C29" s="72" t="s">
+      <c r="C29" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="D29" s="72">
+      <c r="D29" s="80">
         <v>52000</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A30" s="72">
+      <c r="A30" s="80">
         <v>1029</v>
       </c>
-      <c r="B30" s="72" t="s">
+      <c r="B30" s="80" t="s">
         <v>256</v>
       </c>
-      <c r="C30" s="72" t="s">
+      <c r="C30" s="80" t="s">
         <v>231</v>
       </c>
-      <c r="D30" s="72">
+      <c r="D30" s="80">
         <v>48000</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A31" s="72">
+      <c r="A31" s="80">
         <v>1030</v>
       </c>
-      <c r="B31" s="72" t="s">
+      <c r="B31" s="80" t="s">
         <v>257</v>
       </c>
-      <c r="C31" s="72" t="s">
+      <c r="C31" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="D31" s="72">
+      <c r="D31" s="80">
         <v>41000</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A32" s="72">
+      <c r="A32" s="80">
         <v>1031</v>
       </c>
-      <c r="B32" s="72" t="s">
+      <c r="B32" s="80" t="s">
         <v>258</v>
       </c>
-      <c r="C32" s="72" t="s">
+      <c r="C32" s="80" t="s">
         <v>227</v>
       </c>
-      <c r="D32" s="72">
+      <c r="D32" s="80">
         <v>45000</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="72">
+      <c r="A33" s="80">
         <v>1032</v>
       </c>
-      <c r="B33" s="72" t="s">
+      <c r="B33" s="80" t="s">
         <v>259</v>
       </c>
-      <c r="C33" s="72" t="s">
+      <c r="C33" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="D33" s="72">
+      <c r="D33" s="80">
         <v>53000</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="72">
+      <c r="A34" s="80">
         <v>1033</v>
       </c>
-      <c r="B34" s="72" t="s">
+      <c r="B34" s="80" t="s">
         <v>260</v>
       </c>
-      <c r="C34" s="72" t="s">
+      <c r="C34" s="80" t="s">
         <v>231</v>
       </c>
-      <c r="D34" s="72">
+      <c r="D34" s="80">
         <v>49000</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="72">
+      <c r="A35" s="80">
         <v>1034</v>
       </c>
-      <c r="B35" s="72" t="s">
+      <c r="B35" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C35" s="72" t="s">
+      <c r="C35" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="D35" s="72">
+      <c r="D35" s="80">
         <v>42000</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="72">
+      <c r="A36" s="80">
         <v>1035</v>
       </c>
-      <c r="B36" s="72" t="s">
+      <c r="B36" s="80" t="s">
         <v>262</v>
       </c>
-      <c r="C36" s="72" t="s">
+      <c r="C36" s="80" t="s">
         <v>227</v>
       </c>
-      <c r="D36" s="72">
+      <c r="D36" s="80">
         <v>46000</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="72">
+      <c r="A37" s="80">
         <v>1036</v>
       </c>
-      <c r="B37" s="72" t="s">
+      <c r="B37" s="80" t="s">
         <v>263</v>
       </c>
-      <c r="C37" s="72" t="s">
+      <c r="C37" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="D37" s="72">
+      <c r="D37" s="80">
         <v>54000</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="72">
+      <c r="A38" s="80">
         <v>1037</v>
       </c>
-      <c r="B38" s="72" t="s">
+      <c r="B38" s="80" t="s">
         <v>264</v>
       </c>
-      <c r="C38" s="72" t="s">
+      <c r="C38" s="80" t="s">
         <v>231</v>
       </c>
-      <c r="D38" s="72">
+      <c r="D38" s="80">
         <v>50000</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="72">
+      <c r="A39" s="80">
         <v>1038</v>
       </c>
-      <c r="B39" s="72" t="s">
+      <c r="B39" s="80" t="s">
         <v>265</v>
       </c>
-      <c r="C39" s="72" t="s">
+      <c r="C39" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="D39" s="72">
+      <c r="D39" s="80">
         <v>43000</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="72">
+      <c r="A40" s="80">
         <v>1039</v>
       </c>
-      <c r="B40" s="72" t="s">
+      <c r="B40" s="80" t="s">
         <v>266</v>
       </c>
-      <c r="C40" s="72" t="s">
+      <c r="C40" s="80" t="s">
         <v>227</v>
       </c>
-      <c r="D40" s="72">
+      <c r="D40" s="80">
         <v>47000</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="72">
+      <c r="A41" s="80">
         <v>1040</v>
       </c>
-      <c r="B41" s="72" t="s">
+      <c r="B41" s="80" t="s">
         <v>267</v>
       </c>
-      <c r="C41" s="72" t="s">
+      <c r="C41" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="D41" s="72">
+      <c r="D41" s="80">
         <v>55000</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="72">
+      <c r="A42" s="80">
         <v>1041</v>
       </c>
-      <c r="B42" s="72" t="s">
+      <c r="B42" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="C42" s="72" t="s">
+      <c r="C42" s="80" t="s">
         <v>231</v>
       </c>
-      <c r="D42" s="72">
+      <c r="D42" s="80">
         <v>51000</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="72">
+      <c r="A43" s="80">
         <v>1042</v>
       </c>
-      <c r="B43" s="72" t="s">
+      <c r="B43" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="C43" s="72" t="s">
+      <c r="C43" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="D43" s="72">
+      <c r="D43" s="80">
         <v>44000</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="72">
+      <c r="A44" s="80">
         <v>1043</v>
       </c>
-      <c r="B44" s="72" t="s">
+      <c r="B44" s="80" t="s">
         <v>270</v>
       </c>
-      <c r="C44" s="72" t="s">
+      <c r="C44" s="80" t="s">
         <v>227</v>
       </c>
-      <c r="D44" s="72">
+      <c r="D44" s="80">
         <v>48000</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="72">
+      <c r="A45" s="80">
         <v>1044</v>
       </c>
-      <c r="B45" s="72" t="s">
+      <c r="B45" s="80" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="72" t="s">
+      <c r="C45" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="D45" s="72">
+      <c r="D45" s="80">
         <v>56000</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="72">
+      <c r="A46" s="80">
         <v>1045</v>
       </c>
-      <c r="B46" s="72" t="s">
+      <c r="B46" s="80" t="s">
         <v>272</v>
       </c>
-      <c r="C46" s="72" t="s">
+      <c r="C46" s="80" t="s">
         <v>231</v>
       </c>
-      <c r="D46" s="72">
+      <c r="D46" s="80">
         <v>52000</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="72">
+      <c r="A47" s="80">
         <v>1046</v>
       </c>
-      <c r="B47" s="72" t="s">
+      <c r="B47" s="80" t="s">
         <v>273</v>
       </c>
-      <c r="C47" s="72" t="s">
+      <c r="C47" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="D47" s="72">
+      <c r="D47" s="80">
         <v>45000</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="72">
+      <c r="A48" s="80">
         <v>1047</v>
       </c>
-      <c r="B48" s="72" t="s">
+      <c r="B48" s="80" t="s">
         <v>274</v>
       </c>
-      <c r="C48" s="72" t="s">
+      <c r="C48" s="80" t="s">
         <v>227</v>
       </c>
-      <c r="D48" s="72">
+      <c r="D48" s="80">
         <v>49000</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="72">
+      <c r="A49" s="80">
         <v>1048</v>
       </c>
-      <c r="B49" s="72" t="s">
+      <c r="B49" s="80" t="s">
         <v>275</v>
       </c>
-      <c r="C49" s="72" t="s">
+      <c r="C49" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="D49" s="72">
+      <c r="D49" s="80">
         <v>57000</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="72">
+      <c r="A50" s="80">
         <v>1049</v>
       </c>
-      <c r="B50" s="72" t="s">
+      <c r="B50" s="80" t="s">
         <v>276</v>
       </c>
-      <c r="C50" s="72" t="s">
+      <c r="C50" s="80" t="s">
         <v>231</v>
       </c>
-      <c r="D50" s="72">
+      <c r="D50" s="80">
         <v>53000</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="72">
+      <c r="A51" s="80">
         <v>1050</v>
       </c>
-      <c r="B51" s="72" t="s">
+      <c r="B51" s="80" t="s">
         <v>277</v>
       </c>
-      <c r="C51" s="72" t="s">
+      <c r="C51" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="D51" s="72">
+      <c r="D51" s="80">
         <v>46000</v>
       </c>
     </row>
@@ -4496,7 +4593,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B44A88D0-7128-4E96-B95B-AD6F4A5E8B63}">
-  <dimension ref="B2:O11"/>
+  <dimension ref="B2:O15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="5" width="10.81640625" customWidth="1"/>
@@ -4511,20 +4608,20 @@
       <c r="D2" s="60" t="s">
         <v>173</v>
       </c>
-      <c r="F2" s="78" t="s">
+      <c r="F2" s="77" t="s">
         <v>174</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
       <c r="K2" s="60" t="s">
         <v>175</v>
       </c>
-      <c r="M2" s="78" t="s">
+      <c r="M2" s="77" t="s">
         <v>176</v>
       </c>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
     </row>
     <row r="4" spans="2:15" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B4" s="60" t="s">
@@ -4556,7 +4653,10 @@
       <c r="E5" s="59" t="s">
         <v>184</v>
       </c>
-      <c r="F5" s="59"/>
+      <c r="F5" s="59">
+        <f>MATCH(E5,B5:B11,0)</f>
+        <v>3</v>
+      </c>
       <c r="J5" s="46">
         <v>10124</v>
       </c>
@@ -4659,6 +4759,12 @@
     <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="46" t="s">
         <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="L15" t="str">
+        <f>INDEX(J5:M10,4,2)</f>
+        <v>Grapes</v>
       </c>
     </row>
   </sheetData>
@@ -4677,6 +4783,7 @@
   <cols>
     <col min="5" max="5" width="56.453125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="6" spans="5:17" ht="18.5" x14ac:dyDescent="0.45">
@@ -4728,7 +4835,12 @@
       <c r="N8" s="64" t="s">
         <v>200</v>
       </c>
-      <c r="O8" s="65"/>
+      <c r="O8" s="66" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="9" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E9" s="66" t="s">
@@ -4750,7 +4862,12 @@
       <c r="N9" t="s">
         <v>204</v>
       </c>
-      <c r="O9" s="65"/>
+      <c r="O9" s="65" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="10" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E10" s="66" t="s">
@@ -4796,7 +4913,14 @@
       <c r="N11" t="s">
         <v>207</v>
       </c>
-      <c r="O11" s="68"/>
+      <c r="O11" s="68">
+        <f>MATCH(O8,E9:E24,0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q11">
+        <f>MATCH(Q8,E9:E24,0)</f>
+        <v>12</v>
+      </c>
     </row>
     <row r="12" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E12" s="66" t="s">
@@ -4824,7 +4948,14 @@
       <c r="N12" t="s">
         <v>208</v>
       </c>
-      <c r="O12" s="68"/>
+      <c r="O12" s="68">
+        <f>MATCH(O9,F8:L8,0)</f>
+        <v>4</v>
+      </c>
+      <c r="Q12">
+        <f>MATCH(Q9,F8:L8,0)</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="13" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E13" s="66" t="s">
@@ -4868,8 +4999,14 @@
       <c r="N14" t="s">
         <v>211</v>
       </c>
-      <c r="O14" s="67"/>
-      <c r="Q14" s="70"/>
+      <c r="O14" s="67">
+        <f>INDEX(F9:L24,O11,O12)</f>
+        <v>0.24305555555555555</v>
+      </c>
+      <c r="Q14" s="70">
+        <f>INDEX(F9:L24,Q11,Q12)</f>
+        <v>0.28125</v>
+      </c>
     </row>
     <row r="15" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E15" s="66" t="s">
@@ -4911,8 +5048,14 @@
       <c r="N16" t="s">
         <v>213</v>
       </c>
-      <c r="O16" s="67"/>
-      <c r="Q16" s="70"/>
+      <c r="O16" s="67">
+        <f>INDEX(F9:L24,MATCH(O8,E9:E24,0),MATCH(O9,F8:L8,0))</f>
+        <v>0.24305555555555555</v>
+      </c>
+      <c r="Q16" s="70">
+        <f>INDEX(F9:L24,MATCH(Q8,E9:E24,0),MATCH(Q9,F8:L8,0))</f>
+        <v>0.28125</v>
+      </c>
     </row>
     <row r="17" spans="5:15" x14ac:dyDescent="0.35">
       <c r="E17" s="66" t="s">
@@ -5107,11 +5250,6 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O9" xr:uid="{EC1937D0-0817-4B3C-8919-08AE495D2F0C}">
-      <formula1>$D$8:$J$8</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>